--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,6 +1523,112 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118882408</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534339</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6830653</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,6 +1629,1136 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118916568</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91779</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534330</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6830669</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118916494</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>534338</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6830653</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118916501</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>534528</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6830530</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118916502</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>534241</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6830828</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118916548</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>534236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6830834</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118916554</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>534476</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6830559</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118916518</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90276</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534188</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6830952</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118916555</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>534182</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6830957</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118916509</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>534280</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6830750</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118916557</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>534212</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6830851</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916494</v>
+        <v>118916509</v>
       </c>
       <c r="B11" t="n">
-        <v>90504</v>
+        <v>57443</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534338</v>
+        <v>534280</v>
       </c>
       <c r="R11" t="n">
-        <v>6830653</v>
+        <v>6830750</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,7 +1855,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916501</v>
+        <v>118916502</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534528</v>
+        <v>534241</v>
       </c>
       <c r="R12" t="n">
-        <v>6830530</v>
+        <v>6830828</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916502</v>
+        <v>118916557</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>97763</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,43 +1984,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534241</v>
+        <v>534212</v>
       </c>
       <c r="R13" t="n">
-        <v>6830828</v>
+        <v>6830851</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2052,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916548</v>
+        <v>118916501</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,34 +2100,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534236</v>
+        <v>534528</v>
       </c>
       <c r="R14" t="n">
-        <v>6830834</v>
+        <v>6830530</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916554</v>
+        <v>118916518</v>
       </c>
       <c r="B15" t="n">
-        <v>97763</v>
+        <v>90276</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,21 +2217,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534476</v>
+        <v>534188</v>
       </c>
       <c r="R15" t="n">
-        <v>6830559</v>
+        <v>6830952</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916518</v>
+        <v>118916554</v>
       </c>
       <c r="B16" t="n">
-        <v>90276</v>
+        <v>97763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534188</v>
+        <v>534476</v>
       </c>
       <c r="R16" t="n">
-        <v>6830952</v>
+        <v>6830559</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916555</v>
+        <v>118916494</v>
       </c>
       <c r="B17" t="n">
-        <v>97763</v>
+        <v>90504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,25 +2437,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534182</v>
+        <v>534338</v>
       </c>
       <c r="R17" t="n">
-        <v>6830957</v>
+        <v>6830653</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2537,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916509</v>
+        <v>118916548</v>
       </c>
       <c r="B18" t="n">
-        <v>57443</v>
+        <v>78484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534280</v>
+        <v>534236</v>
       </c>
       <c r="R18" t="n">
-        <v>6830750</v>
+        <v>6830834</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,7 +2649,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916557</v>
+        <v>118916555</v>
       </c>
       <c r="B19" t="n">
         <v>97763</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534212</v>
+        <v>534182</v>
       </c>
       <c r="R19" t="n">
-        <v>6830851</v>
+        <v>6830957</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>118882408</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916568</v>
+        <v>118916548</v>
       </c>
       <c r="B10" t="n">
-        <v>91779</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,25 +1643,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534330</v>
+        <v>534236</v>
       </c>
       <c r="R10" t="n">
-        <v>6830669</v>
+        <v>6830834</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916509</v>
+        <v>118916494</v>
       </c>
       <c r="B11" t="n">
-        <v>57443</v>
+        <v>90511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534280</v>
+        <v>534338</v>
       </c>
       <c r="R11" t="n">
-        <v>6830750</v>
+        <v>6830653</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916557</v>
+        <v>118916554</v>
       </c>
       <c r="B13" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534212</v>
+        <v>534476</v>
       </c>
       <c r="R13" t="n">
-        <v>6830851</v>
+        <v>6830559</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916501</v>
+        <v>118916518</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>90283</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,43 +2096,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534528</v>
+        <v>534188</v>
       </c>
       <c r="R14" t="n">
-        <v>6830530</v>
+        <v>6830952</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2164,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2174,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916518</v>
+        <v>118916557</v>
       </c>
       <c r="B15" t="n">
-        <v>90276</v>
+        <v>97770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,21 +2212,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2241,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534188</v>
+        <v>534212</v>
       </c>
       <c r="R15" t="n">
-        <v>6830952</v>
+        <v>6830851</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916554</v>
+        <v>118916555</v>
       </c>
       <c r="B16" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534476</v>
+        <v>534182</v>
       </c>
       <c r="R16" t="n">
-        <v>6830559</v>
+        <v>6830957</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916494</v>
+        <v>118916568</v>
       </c>
       <c r="B17" t="n">
-        <v>90504</v>
+        <v>91786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,25 +2432,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534338</v>
+        <v>534330</v>
       </c>
       <c r="R17" t="n">
-        <v>6830653</v>
+        <v>6830669</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916548</v>
+        <v>118916509</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,21 +2548,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534236</v>
+        <v>534280</v>
       </c>
       <c r="R18" t="n">
-        <v>6830834</v>
+        <v>6830750</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2612,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916555</v>
+        <v>118916501</v>
       </c>
       <c r="B19" t="n">
-        <v>97763</v>
+        <v>57290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2661,38 +2656,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534182</v>
+        <v>534528</v>
       </c>
       <c r="R19" t="n">
-        <v>6830957</v>
+        <v>6830530</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1631,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916548</v>
+        <v>118916509</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,21 +1647,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534236</v>
+        <v>534280</v>
       </c>
       <c r="R10" t="n">
-        <v>6830834</v>
+        <v>6830750</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916494</v>
+        <v>118916568</v>
       </c>
       <c r="B11" t="n">
-        <v>90511</v>
+        <v>91786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534338</v>
+        <v>534330</v>
       </c>
       <c r="R11" t="n">
-        <v>6830653</v>
+        <v>6830669</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,7 +1855,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916502</v>
+        <v>118916501</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534241</v>
+        <v>534528</v>
       </c>
       <c r="R12" t="n">
-        <v>6830828</v>
+        <v>6830530</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,7 +1972,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916554</v>
+        <v>118916557</v>
       </c>
       <c r="B13" t="n">
         <v>97770</v>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534476</v>
+        <v>534212</v>
       </c>
       <c r="R13" t="n">
-        <v>6830559</v>
+        <v>6830851</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916518</v>
+        <v>118916555</v>
       </c>
       <c r="B14" t="n">
-        <v>90283</v>
+        <v>97770</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534188</v>
+        <v>534182</v>
       </c>
       <c r="R14" t="n">
-        <v>6830952</v>
+        <v>6830957</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916557</v>
+        <v>118916548</v>
       </c>
       <c r="B15" t="n">
-        <v>97770</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,25 +2208,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534212</v>
+        <v>534236</v>
       </c>
       <c r="R15" t="n">
-        <v>6830851</v>
+        <v>6830834</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,7 +2308,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916555</v>
+        <v>118916554</v>
       </c>
       <c r="B16" t="n">
         <v>97770</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534182</v>
+        <v>534476</v>
       </c>
       <c r="R16" t="n">
-        <v>6830957</v>
+        <v>6830559</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916568</v>
+        <v>118916518</v>
       </c>
       <c r="B17" t="n">
-        <v>91786</v>
+        <v>90283</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,21 +2436,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534330</v>
+        <v>534188</v>
       </c>
       <c r="R17" t="n">
-        <v>6830669</v>
+        <v>6830952</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916509</v>
+        <v>118916494</v>
       </c>
       <c r="B18" t="n">
-        <v>57443</v>
+        <v>90511</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2548,21 +2548,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534280</v>
+        <v>534338</v>
       </c>
       <c r="R18" t="n">
-        <v>6830750</v>
+        <v>6830653</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916501</v>
+        <v>118916502</v>
       </c>
       <c r="B19" t="n">
         <v>57290</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534528</v>
+        <v>534241</v>
       </c>
       <c r="R19" t="n">
-        <v>6830530</v>
+        <v>6830828</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1858,11 +1858,11 @@
         <v>118916501</v>
       </c>
       <c r="B12" t="n">
-        <v>57292</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2423,11 +2423,11 @@
         <v>118916502</v>
       </c>
       <c r="B17" t="n">
-        <v>57292</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,11 +1648,6 @@
       </c>
       <c r="E10" t="n">
         <v>219790</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1746,7 +1741,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,11 +1755,6 @@
       </c>
       <c r="E11" t="n">
         <v>219790</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2087,7 +2077,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,11 +2091,6 @@
       </c>
       <c r="E14" t="n">
         <v>219790</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,6 +1648,11 @@
       </c>
       <c r="E10" t="n">
         <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1741,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,6 +1760,11 @@
       </c>
       <c r="E11" t="n">
         <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2077,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,6 +2101,11 @@
       </c>
       <c r="E14" t="n">
         <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1634,7 +1634,7 @@
         <v>118916557</v>
       </c>
       <c r="B10" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>118916555</v>
       </c>
       <c r="B11" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>118916554</v>
       </c>
       <c r="B14" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>118916501</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>118916502</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 45009-2019 artfynd.xlsx
+++ b/artfynd/A 45009-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,10 +1418,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112606323</v>
+        <v>118882408</v>
       </c>
       <c r="B8" t="n">
-        <v>78919</v>
+        <v>90513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,37 +1434,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öratjärn, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534487</v>
+        <v>534339</v>
       </c>
       <c r="R8" t="n">
-        <v>6830571</v>
+        <v>6830653</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,17 +1491,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,28 +1505,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118882408</v>
+        <v>118916557</v>
       </c>
       <c r="B9" t="n">
-        <v>90513</v>
+        <v>98264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,41 +1536,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534339</v>
+        <v>534212</v>
       </c>
       <c r="R9" t="n">
-        <v>6830653</v>
+        <v>6830851</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1601,18 +1597,27 @@
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1631,7 +1636,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916557</v>
+        <v>118916555</v>
       </c>
       <c r="B10" t="n">
         <v>98264</v>
@@ -1671,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534212</v>
+        <v>534182</v>
       </c>
       <c r="R10" t="n">
-        <v>6830851</v>
+        <v>6830957</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1706,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1721,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916555</v>
+        <v>118916501</v>
       </c>
       <c r="B11" t="n">
-        <v>98264</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,38 +1760,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534182</v>
+        <v>534528</v>
       </c>
       <c r="R11" t="n">
-        <v>6830957</v>
+        <v>6830530</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916501</v>
+        <v>118916509</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57445</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,39 +1881,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534528</v>
+        <v>534280</v>
       </c>
       <c r="R12" t="n">
-        <v>6830530</v>
+        <v>6830750</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916509</v>
+        <v>118916554</v>
       </c>
       <c r="B13" t="n">
-        <v>57445</v>
+        <v>98264</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,25 +1989,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2012,10 +2017,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534280</v>
+        <v>534476</v>
       </c>
       <c r="R13" t="n">
-        <v>6830750</v>
+        <v>6830559</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2047,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916554</v>
+        <v>118916548</v>
       </c>
       <c r="B14" t="n">
-        <v>98264</v>
+        <v>78493</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,25 +2101,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534476</v>
+        <v>534236</v>
       </c>
       <c r="R14" t="n">
-        <v>6830559</v>
+        <v>6830834</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916548</v>
+        <v>118916494</v>
       </c>
       <c r="B15" t="n">
-        <v>78493</v>
+        <v>90513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,21 +2217,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2241,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534236</v>
+        <v>534338</v>
       </c>
       <c r="R15" t="n">
-        <v>6830834</v>
+        <v>6830653</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2271,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916494</v>
+        <v>118916502</v>
       </c>
       <c r="B16" t="n">
-        <v>90513</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,34 +2329,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534338</v>
+        <v>534241</v>
       </c>
       <c r="R16" t="n">
-        <v>6830653</v>
+        <v>6830828</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2383,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2403,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916502</v>
+        <v>118916518</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>90285</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,43 +2442,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534241</v>
+        <v>534188</v>
       </c>
       <c r="R17" t="n">
-        <v>6830828</v>
+        <v>6830952</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916518</v>
+        <v>118916568</v>
       </c>
       <c r="B18" t="n">
-        <v>90285</v>
+        <v>91791</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,21 +2558,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2582,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534188</v>
+        <v>534330</v>
       </c>
       <c r="R18" t="n">
-        <v>6830952</v>
+        <v>6830669</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2612,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2627,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,118 +2651,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>118916568</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91791</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>534330</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6830669</v>
-      </c>
-      <c r="S19" t="n">
-        <v>25</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
